--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/HRM/post DFS_HRM-2031-0212/Panel 7/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU05_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/HRM/post DFS_HRM-2031-0212/Panel 7/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU05_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.14663</v>
+        <v>16.97717</v>
       </c>
       <c r="D2" t="n">
-        <v>16.92236</v>
+        <v>16.73862</v>
       </c>
       <c r="E2" t="n">
-        <v>16.95985</v>
+        <v>16.90816</v>
       </c>
       <c r="F2" t="n">
-        <v>42.65185</v>
+        <v>42.17433</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05074</v>
+        <v>0.05166</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84982</v>
+        <v>1.84634</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.34293</v>
+        <v>17.24229</v>
       </c>
       <c r="D3" t="n">
-        <v>16.85245</v>
+        <v>17.11367</v>
       </c>
       <c r="E3" t="n">
-        <v>17.17262</v>
+        <v>17.16764</v>
       </c>
       <c r="F3" t="n">
-        <v>43.66211</v>
+        <v>42.57358</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05123</v>
+        <v>0.05151</v>
       </c>
       <c r="H3" t="n">
-        <v>1.85207</v>
+        <v>1.87055</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.22706</v>
+        <v>17.27037</v>
       </c>
       <c r="D4" t="n">
-        <v>17.09901</v>
+        <v>16.72568</v>
       </c>
       <c r="E4" t="n">
-        <v>16.81267</v>
+        <v>17.18</v>
       </c>
       <c r="F4" t="n">
-        <v>43.78812</v>
+        <v>43.16527</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05258</v>
+        <v>0.05197</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83858</v>
+        <v>1.87834</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.94297</v>
+        <v>16.85298</v>
       </c>
       <c r="D6" t="n">
-        <v>16.13873</v>
+        <v>16.17273</v>
       </c>
       <c r="E6" t="n">
-        <v>16.73705</v>
+        <v>16.71611</v>
       </c>
       <c r="F6" t="n">
-        <v>22.42015</v>
+        <v>22.03307</v>
       </c>
       <c r="G6" t="n">
-        <v>34.30362</v>
+        <v>35.13911</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.02825</v>
+        <v>17.26116</v>
       </c>
       <c r="D7" t="n">
-        <v>16.28666</v>
+        <v>16.22951</v>
       </c>
       <c r="E7" t="n">
-        <v>16.86598</v>
+        <v>17.03395</v>
       </c>
       <c r="F7" t="n">
-        <v>22.13059</v>
+        <v>21.92443</v>
       </c>
       <c r="G7" t="n">
-        <v>34.18704</v>
+        <v>35.49528</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.17391</v>
+        <v>16.97564</v>
       </c>
       <c r="D8" t="n">
-        <v>16.34647</v>
+        <v>16.19748</v>
       </c>
       <c r="E8" t="n">
-        <v>16.59563</v>
+        <v>16.57798</v>
       </c>
       <c r="F8" t="n">
-        <v>22.08124</v>
+        <v>22.83675</v>
       </c>
       <c r="G8" t="n">
-        <v>34.64357</v>
+        <v>34.75597</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.61374</v>
+        <v>0.60956</v>
       </c>
       <c r="D10" t="n">
-        <v>1.13661</v>
+        <v>1.12077</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.61316</v>
+        <v>0.60475</v>
       </c>
       <c r="D11" t="n">
-        <v>1.12629</v>
+        <v>1.12713</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.61538</v>
+        <v>0.61286</v>
       </c>
       <c r="D12" t="n">
-        <v>1.10868</v>
+        <v>1.12798</v>
       </c>
     </row>
   </sheetData>
